--- a/Codelist Excel Files and Conversion Templates to XML/verificationOutcome.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/verificationOutcome.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="9200" yWindow="3280" windowWidth="39400" windowHeight="24940" tabRatio="500" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="DictionaryName" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Definitions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="AssociatedElements" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="AlternateNames" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Lists" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DictionaryName" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AssociatedElements" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AlternateNames" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -995,7 +995,7 @@
       <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1202,10 +1202,31 @@
         <f>IF(ISNA(VLOOKUP(B6,AssociatedElements!B$2:B2944,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
-      <c r="C6" s="16" t="n"/>
-      <c r="D6" s="16" t="n"/>
-      <c r="E6" s="17" t="n"/>
-      <c r="G6" s="9" t="n"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>inconclusive</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>Inconclusive</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>The check was run and its evidence cannot decide the criterion - for example a record that does not meet the condition on which the criterion's reading rests, or one that shows no feature to measure. Neither satisfied nor not satisfied, and no concession is made: the criterion is left open. Bound to diggs:AcceptanceCheck only.</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>DIGGS</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2">
@@ -1719,7 +1740,16 @@
         <f>IF(ISNA(VLOOKUP(B9,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B9" s="2" t="n"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>inconclusive</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>//diggs:AcceptanceCheck/diggs:outcome</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10">
